--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEVADA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEVADA_2017.xlsx
@@ -2137,7 +2137,7 @@
         <v>155</v>
       </c>
       <c r="D99">
-        <v>0.009208103130755065</v>
+        <v>0.009208103130755063</v>
       </c>
     </row>
     <row r="100">
@@ -2479,7 +2479,7 @@
         <v>16</v>
       </c>
       <c r="D118">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="119">
@@ -2767,7 +2767,7 @@
         <v>16</v>
       </c>
       <c r="D134">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="135">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C165">
@@ -5035,7 +5035,7 @@
         <v>16</v>
       </c>
       <c r="D260">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="261">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C285">
@@ -6547,7 +6547,7 @@
         <v>16</v>
       </c>
       <c r="D344">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="345">
@@ -10723,7 +10723,7 @@
         <v>16</v>
       </c>
       <c r="D576">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="577">
@@ -11011,7 +11011,7 @@
         <v>16</v>
       </c>
       <c r="D592">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="593">
@@ -11443,7 +11443,7 @@
         <v>16</v>
       </c>
       <c r="D616">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="617">
@@ -12901,7 +12901,7 @@
         <v>16</v>
       </c>
       <c r="D697">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="698">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C788">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C813">
@@ -20173,7 +20173,7 @@
         <v>16</v>
       </c>
       <c r="D1101">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="1102">
@@ -23017,7 +23017,7 @@
         <v>16</v>
       </c>
       <c r="D1259">
-        <v>0.0009505138715618131</v>
+        <v>0.0009505138715618132</v>
       </c>
     </row>
     <row r="1260">
